--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_16-10-2025.xlsx
@@ -528,17 +528,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -576,25 +576,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -639,17 +639,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -687,25 +687,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -750,17 +750,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -798,25 +798,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -861,17 +861,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -909,25 +909,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -972,17 +972,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1020,25 +1020,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1131,25 +1131,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1194,17 +1194,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1242,25 +1242,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1353,25 +1353,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,25 +1464,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1575,25 +1575,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1686,25 +1686,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1797,25 +1797,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1908,25 +1908,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2019,25 +2019,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2130,25 +2130,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff6e6d3e9e5+80021]
+	GetHandleVerifier [0x0x7ff6e6d3ea40+80112]
+	(No symbol) [0x0x7ff6e6ac060f]
+	(No symbol) [0x0x7ff6e6b18854]
+	(No symbol) [0x0x7ff6e6b18b1c]
+	(No symbol) [0x0x7ff6e6b6c927]
+	(No symbol) [0x0x7ff6e6b4126f]
+	(No symbol) [0x0x7ff6e6b6968a]
+	(No symbol) [0x0x7ff6e6b41003]
+	(No symbol) [0x0x7ff6e6b095d1]
+	(No symbol) [0x0x7ff6e6b0a3f3]
+	GetHandleVerifier [0x0x7ff6e6ffdd8d+2960445]
+	GetHandleVerifier [0x0x7ff6e6ff804a+2936570]
+	GetHandleVerifier [0x0x7ff6e7018a87+3070263]
+	GetHandleVerifier [0x0x7ff6e6d584ce+185214]
+	GetHandleVerifier [0x0x7ff6e6d5ff1f+216527]
+	GetHandleVerifier [0x0x7ff6e6d47c24+117460]
+	GetHandleVerifier [0x0x7ff6e6d47ddf+117903]
+	GetHandleVerifier [0x0x7ff6e6d2dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
